--- a/AI Audit Log_Mai Xuan Tri.xlsx
+++ b/AI Audit Log_Mai Xuan Tri.xlsx
@@ -7,7 +7,9 @@
     <workbookView windowWidth="28800" windowHeight="11580"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Week1" sheetId="1" r:id="rId1"/>
+    <sheet name="Week2" sheetId="2" r:id="rId2"/>
+    <sheet name="Week3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>STT</t>
   </si>
@@ -96,6 +98,58 @@
   </si>
   <si>
     <t>Đây là ví dụ AI xử lý tốt sự mơ hồ (ambiguity). Tôi chọn "Kiến trúc phần mềm" — xác nhận rằng prompt cần đủ cụ thể để AI trả lời đúng hướng.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition + Abstraction</t>
+  </si>
+  <si>
+    <t>You are required to design a design-level Class Diagram for the car rental system...
+[Yêu cầu thiết kế Class Diagram với User, Customer, Staff, Car, Booking, Payment, Repository Pattern]</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh ra PlantUML Class Diagram đầy đủ với inheritance, association, composition, dependency và các enum trạng thái.
+Quyết định: Chấp nhận diagram ban đầu, sau đó tiến hành review từng thành phần.</t>
+  </si>
+  <si>
+    <t>Tại sao StaffRole lại có AGENT và MECHANIC?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI thừa nhận đã tự thêm AGENT và MECHANIC mà không có cơ sở từ đề bài — đây là over-assumption.
+Quyết định: Xóa enum StaffRole hoặc thay bằng staffRole: String để linh hoạt hơn.</t>
+  </si>
+  <si>
+    <t>Tại sao PaymentService lại phụ thuộc trực tiếp vào các lớp triển khai cụ thể như PaymentRepository và BookingRepository thay vì các Interface?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận đây là vi phạm Dependency Inversion Principle (DIP). Đề xuất PaymentService phụ thuộc vào IRepository&lt;Payment&gt; và IRepository&lt;Booking&gt; thay vì class cụ thể.
+Quyết định: Sửa dependency sang interface — loosely coupled, dễ test/mock.</t>
+  </si>
+  <si>
+    <t>Trong lớp Payment có process() và refund(), trong PaymentService cũng có processDeposit() và processRefund(). Như vậy có bị trùng lặp trách nhiệm không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận vi phạm SRP. Entity Payment chỉ nên giữ state (markAsCompleted, markAsFailed). Business logic thuộc về PaymentService.
+Quyết định: Xóa process() và refund() khỏi Payment entity.</t>
+  </si>
+  <si>
+    <t>Abstraction + Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Thuộc tính status: CarStatus trong Car hiện là Enum. Khi chuyển đổi trạng thái xe có thể phát sinh nhiều logic phức tạp...</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất State Pattern — mỗi trạng thái (AvailableState, RentedState...) thành class riêng implement ICarState, tránh if/switch khổng lồ trong Car.
+Quyết định: Ghi nhận State Pattern là hướng nâng cao, có thể áp dụng trong implementation. Tại diagram giữ ghi chú.</t>
+  </si>
+  <si>
+    <t>Decomposition + Abstraction</t>
+  </si>
+  <si>
+    <t>Thuộc tính rentalHistory: List&lt;Booking&gt; trong Customer khi kết nối DB có hợp lý không? Có nên bỏ và dùng findByCustomerId() của BookingRepository không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích 3 hướng: (1) Xóa hoàn toàn dùng Repository, (2) Giữ lazy loading, (3) Xóa khỏi Entity, xử lý trong BookingService. Khuyến nghị Hướng 3.
+Quyết định: Xóa rentalHistory khỏi Customer, thêm BookingService để tách biệt trách nhiệm truy vấn.</t>
   </si>
 </sst>
 </file>
@@ -108,7 +162,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +186,17 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -300,7 +365,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,12 +380,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEEF2F7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5F5E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9E7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -506,7 +601,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -552,6 +647,21 @@
       <top/>
       <bottom style="medium">
         <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -693,137 +803,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,34 +943,52 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1396,7 +1524,7 @@
     <col min="4" max="4" width="63.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="102.75" spans="1:4">
+    <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1411,178 +1539,178 @@
       </c>
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:4">
-      <c r="A2" s="3">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="8"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" ht="15.75" spans="1:4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="53" customHeight="1" spans="1:4">
-      <c r="A6" s="3"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1" spans="1:4">
-      <c r="A7" s="10">
+      <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="51" customHeight="1" spans="1:4">
-      <c r="A8" s="10"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6" t="s">
+      <c r="A8" s="3"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
-      <c r="A9" s="10"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="8"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10" ht="15.75" spans="1:4">
-      <c r="A10" s="10"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1" spans="1:4">
-      <c r="A11" s="10"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="39.75" customHeight="1" spans="1:4">
-      <c r="A12" s="3">
+      <c r="A12" s="6">
         <v>3</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" ht="53" customHeight="1" spans="1:4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="6" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="8"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" ht="15.75" spans="1:4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4" t="s">
+      <c r="A15" s="6"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:4">
-      <c r="A16" s="3"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4">
-      <c r="A17" s="10">
+      <c r="A17" s="3">
         <v>4</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" ht="26.25" spans="1:4">
-      <c r="A18" s="10"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="6" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" ht="15.75" spans="1:4">
-      <c r="A19" s="10"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="8"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" ht="15.75" spans="1:4">
-      <c r="A20" s="10"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="11" t="s">
+      <c r="A20" s="3"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" ht="39" customHeight="1" spans="1:4">
-      <c r="A21" s="10"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="12" t="s">
+      <c r="A21" s="3"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1600,4 +1728,130 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="35.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="51.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="96" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="51.75" spans="1:4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" ht="51.75" spans="1:4">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="51.75" spans="1:4">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" ht="51" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="63.75" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" ht="51" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/AI Audit Log_Mai Xuan Tri.xlsx
+++ b/AI Audit Log_Mai Xuan Tri.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580"/>
+    <workbookView windowWidth="28800" windowHeight="11580" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Week1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>STT</t>
   </si>
@@ -150,6 +150,162 @@
   <si>
     <t>Phản hồi: AI phân tích 3 hướng: (1) Xóa hoàn toàn dùng Repository, (2) Giữ lazy loading, (3) Xóa khỏi Entity, xử lý trong BookingService. Khuyến nghị Hướng 3.
 Quyết định: Xóa rentalHistory khỏi Customer, thêm BookingService để tách biệt trách nhiệm truy vấn.</t>
+  </si>
+  <si>
+    <t>Region Management</t>
+  </si>
+  <si>
+    <t>Gen class diagram cho Region Management, thêm lớp Repository vào — gồm các entity Region, Branch, Employee, BranchRequest và các lớp IRegionRepository, IBranchRepository, IUnitOfWork, RegionService, RegionController</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh ra Mermaid + PlantUML Class Diagram đầy đủ 4 tầng: Domain Entities, Repository Interfaces, Service, Controller.
+Quyết định: Chấp nhận diagram ban đầu, tiến hành review từng tầng.</t>
+  </si>
+  <si>
+    <t>Liệt kê các entity chính cần có trong Domain layer — có cần EmployeeBranchRequest không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận cần Region, Branch, Employee, BranchRequest, EmployeeBranchRequest để track luồng duyệt yêu cầu chuyển chi nhánh.
+Quyết định: Giữ EmployeeBranchRequest — dùng RequestStatus enum Pending/Approved/Rejected.</t>
+  </si>
+  <si>
+    <t>Tại sao RegionService lại phụ thuộc trực tiếp vào UnitOfWork class thay vì IUnitOfWork interface?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận đây là vi phạm Dependency Inversion Principle (DIP). Đề xuất RegionService phụ thuộc IUnitOfWork thay vì class cụ thể.
+Quyết định: Sửa dependency sang interface — loosely coupled, dễ test/mock.</t>
+  </si>
+  <si>
+    <t>IUnitOfWork nên aggregate tất cả repositories hay chỉ những repo liên quan đến module?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất IUnitOfWork chứa Regions, Branches, Employees, BranchRequests — đủ dùng cho RegionService mà không bloat interface.
+Quyết định: Chấp nhận. UnitOfWork giữ _db private — Service không truy cập ApplicationDbContext trực tiếp.</t>
+  </si>
+  <si>
+    <t>Thuộc tính Branches: ICollection&lt;Branch&gt; trong Region khi kết nối DB có hợp lý không? Có nên bỏ và dùng GetBranchesByRegionIdAsync() của IBranchRepository không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích 3 hướng: (1) Xóa hoàn toàn dùng Repository, (2) Giữ lazy loading EF Core, (3) Xóa khỏi Entity, xử lý trong RegionService. Khuyến nghị Hướng 3.
+Quyết định: Xóa collection nav property khỏi domain entity, thêm query method vào IBranchRepository.</t>
+  </si>
+  <si>
+    <t>Gen Mermaid Sequence Diagram cho luồng CreateBranchAddRequest từ Controller xuống DB</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh Sequence Diagram: User → RegionController → RegionService → IUnitOfWork → BranchRepository → EF Core DbContext, thể hiện rõ async/await.
+Quyết định: Chấp nhận. Dùng để onboard dev mới và làm tài liệu kỹ thuật.</t>
+  </si>
+  <si>
+    <t>Employee Management</t>
+  </si>
+  <si>
+    <t>Gen class diagram cho Employee Management — gồm Employee, Role, Branch và các lớp IEmployeeRepository, IUnitOfWork, EmployeeService, EmployeeController</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh Mermaid + PlantUML Class Diagram với Employee có quan hệ nullable FK đến Branch (chưa gán chi nhánh) và FK đến Role.
+Quyết định: Chấp nhận diagram ban đầu, tiến hành review quan hệ và field types.</t>
+  </si>
+  <si>
+    <t>Employee có bao nhiêu role? Role có phải là enum cứng không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất Role là bảng FK (RoleID: string) thay vì enum — linh hoạt hơn khi thêm role mới không cần migration.
+Quyết định: Dùng staffRole: String — tránh coupling với enum khi nghiệp vụ thay đổi.</t>
+  </si>
+  <si>
+    <t>Tại sao EmployeeService phụ thuộc EmployeeRepository class thay vì IEmployeeRepository interface?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận vi phạm DIP. Đề xuất EmployeeService inject IUnitOfWork chứa IEmployeeRepository thay vì repo class cụ thể.
+Quyết định: Sửa dependency sang interface — đồng nhất pattern với RegionService.</t>
+  </si>
+  <si>
+    <t>IEmployeeRepository cần những method tìm kiếm nào? Có cần GetByRegionAsync, GetByBranchAsync, GetByRoleAsync không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận cần GetByBranchAsync(), GetByRegionAsync(), GetByRoleAsync() và UpdateBranchAssignmentAsync() để tách query phức tạp vào repo.
+Quyết định: Chấp nhận. Service chỉ gọi interface — không viết raw LINQ trong Service.</t>
+  </si>
+  <si>
+    <t>Employee entity có nên giữ List&lt;Booking&gt; history không? Khi kết nối DB có hợp lý không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI xác nhận vi phạm SRP — Entity chỉ nên giữ state. Business query thuộc EmployeeService.GetHistoryAsync().
+Quyết định: Xóa rentalHistory khỏi Employee entity — tách biệt trách nhiệm truy vấn vào Service layer.</t>
+  </si>
+  <si>
+    <t>Gen PlantUML diagram thêm EmployeeBranchRequest — thể hiện luồng duyệt yêu cầu chuyển chi nhánh</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh PlantUML với EmployeeBranchRequest có RequestStatus: Pending/Approved/Rejected, quan hệ đến Employee và Branch.
+Quyết định: Chấp nhận. Đồng bộ interface IEmployeeRepository với IUnitOfWork của Region Management.</t>
+  </si>
+  <si>
+    <t>Booking Management</t>
+  </si>
+  <si>
+    <t>Gen class diagram cho Booking Management — gồm Booking, Payment, Customer, Car và các lớp IBookingRepository, IPaymentRepository, BookingService, BookingController</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh Mermaid + PlantUML Class Diagram với quan hệ 1 Booking : 1 Payment, BookingStatus và PaymentStatus là enum riêng biệt.
+Quyết định: Chấp nhận diagram ban đầu, tiến hành review từng thành phần.</t>
+  </si>
+  <si>
+    <t>BookingStatus và PaymentStatus nên là enum riêng hay dùng chung 1 enum?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất enum riêng: BookingStatus (Pending/Confirmed/Cancelled/Completed) và PaymentStatus (Unpaid/Deposited/Paid/Refunded) — tránh coupling giữa trạng thái đặt xe và thanh toán.
+Quyết định: Giữ 2 enum riêng — mỗi enum phản ánh đúng vòng đời của entity tương ứng.</t>
+  </si>
+  <si>
+    <t>TotalPrice trong Booking tính theo số ngày hay fix cứng? Nên tính ở đâu — entity hay service?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích: tính trong Service (BookingService.CalculateTotalPrice()) nhận Car.DailyRate và số ngày — tránh logic trong entity constructor.
+Quyết định: Xóa computed property khỏi Booking entity, thêm method tính giá vào BookingService.</t>
+  </si>
+  <si>
+    <t>Gen Mermaid Sequence Diagram cho luồng Booking → Payment: đặt cọc và thanh toán đủ</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh Sequence Diagram 2 bước: (1) Customer đặt xe → BookingService tạo Booking + Payment Unpaid; (2) Customer thanh toán → PaymentService cập nhật PaymentStatus Paid → BookingService confirm.
+Quyết định: Chấp nhận. Minh họa rõ 2 transaction riêng biệt.</t>
+  </si>
+  <si>
+    <t>Car Management</t>
+  </si>
+  <si>
+    <t>Gen class diagram cho Car Management — gồm Car, CarBrand, CarModel, CarCategory và các lớp ICarRepository, CarService, CarController</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh Mermaid + PlantUML Class Diagram với CarStatus enum: Available/Rented/Maintenance/Retired, quan hệ Car đến Branch.
+Quyết định: Chấp nhận diagram ban đầu, tiến hành review CarStatus và StaffRole.</t>
+  </si>
+  <si>
+    <t>ICarRepository cần những method nào để tìm theo branch, status, category?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất GetAvailableByBranchAsync(), GetByStatusAsync(), GetByCategoryAsync(), UpdateStatusAsync() — tách update status riêng tránh load toàn bộ Car object.
+Quyết định: Chấp nhận. UpdateStatusAsync() nhận carId + newStatus — tối ưu DB round-trip.</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI đề xuất State Pattern — mỗi trạng thái (AvailableState, RentedState...) thành class riêng implement ICarState, tránh if/switch khổng lồ trong Car.
+Quyết định: Ghi nhận State Pattern là hướng nâng cao, có thể áp dụng trong implementation. Tại diagram giữ enum + ghi chú.</t>
+  </si>
+  <si>
+    <t>Car entity có nên có field Latitude, Longitude để track vị trí xe không?</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích: nếu cần track real-time thì nên tách sang CarLocation entity riêng (CarID, Lat, Lng, UpdatedAt) — tránh bloat Car entity với data thay đổi liên tục.
+Quyết định: Tách CarLocation entity riêng — thêm ICarLocationRepository vào IUnitOfWork nếu cần.</t>
+  </si>
+  <si>
+    <t>Gen Mermaid Sequence Diagram cho luồng đặt xe: kiểm tra Car available → tạo Booking → cập nhật CarStatus</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh Sequence Diagram: Customer → BookingController → BookingService → ICarRepository.GetAvailableByBranchAsync() → tạo Booking → CarService.UpdateStatusAsync(Rented).
+Quyết định: Chấp nhận. Luồng thể hiện rõ 2 service phối hợp qua UnitOfWork chung.</t>
   </si>
 </sst>
 </file>
@@ -162,7 +318,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +347,54 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1E4620"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7D5500"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7B2400"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -365,7 +569,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,6 +620,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -601,7 +835,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -662,6 +896,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C4D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C4D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C4D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C4D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB8C4D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C4D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8C4D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C4D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C4D0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -803,137 +1076,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -967,28 +1240,60 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1542,43 +1847,43 @@
       <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:4">
       <c r="A3" s="6"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="6"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="15"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="27"/>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="6"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="11" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="23" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="53" customHeight="1" spans="1:4">
       <c r="A6" s="6"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1586,43 +1891,43 @@
       <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="51" customHeight="1" spans="1:4">
       <c r="A8" s="3"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="3"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="15"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="27"/>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="3"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="11" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="23" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1" spans="1:4">
       <c r="A11" s="3"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1630,43 +1935,43 @@
       <c r="A12" s="6">
         <v>3</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" ht="53" customHeight="1" spans="1:4">
       <c r="A13" s="6"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13" t="s">
+      <c r="B13" s="25"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="6"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="15"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="27"/>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="6"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11" t="s">
+      <c r="B15" s="26"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="23" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:4">
       <c r="A16" s="6"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12" t="s">
+      <c r="B16" s="28"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1674,43 +1979,43 @@
       <c r="A17" s="3">
         <v>4</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" ht="26.25" spans="1:4">
       <c r="A18" s="3"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" ht="15.75" spans="1:4">
       <c r="A19" s="3"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="15"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="27"/>
     </row>
     <row r="20" ht="15.75" spans="1:4">
       <c r="A20" s="3"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="17" t="s">
+      <c r="B20" s="26"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="29" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" ht="39" customHeight="1" spans="1:4">
       <c r="A21" s="3"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="18" t="s">
+      <c r="B21" s="28"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1744,15 +2049,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="35.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="51.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1850,7 +2155,381 @@
         <v>37</v>
       </c>
     </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" ht="60" spans="1:4">
+      <c r="A9" s="14">
+        <v>1</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" ht="48" spans="1:4">
+      <c r="A10" s="17">
+        <v>2</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" ht="48" spans="1:4">
+      <c r="A11" s="14">
+        <v>3</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" ht="48" spans="1:4">
+      <c r="A12" s="17">
+        <v>4</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" ht="48" spans="1:4">
+      <c r="A13" s="14">
+        <v>5</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" ht="48" spans="1:4">
+      <c r="A14" s="17">
+        <v>6</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" ht="48" spans="1:4">
+      <c r="A16" s="17">
+        <v>1</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" ht="48" spans="1:4">
+      <c r="A17" s="14">
+        <v>2</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" ht="48" spans="1:4">
+      <c r="A18" s="17">
+        <v>3</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" ht="48" spans="1:4">
+      <c r="A19" s="14">
+        <v>4</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" ht="48" spans="1:4">
+      <c r="A20" s="17">
+        <v>5</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" ht="48" spans="1:4">
+      <c r="A21" s="14">
+        <v>6</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" ht="48" spans="1:4">
+      <c r="A23" s="14">
+        <v>1</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" ht="48" spans="1:4">
+      <c r="A24" s="17">
+        <v>2</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" ht="48" spans="1:4">
+      <c r="A25" s="14">
+        <v>3</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" ht="48" spans="1:4">
+      <c r="A26" s="17">
+        <v>4</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" ht="48" spans="1:4">
+      <c r="A27" s="14">
+        <v>5</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" ht="48" spans="1:4">
+      <c r="A28" s="17">
+        <v>6</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" ht="48" spans="1:4">
+      <c r="A30" s="17">
+        <v>1</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" ht="36" spans="1:4">
+      <c r="A31" s="14">
+        <v>2</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" ht="48" spans="1:4">
+      <c r="A32" s="17">
+        <v>3</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" ht="60" spans="1:4">
+      <c r="A33" s="14">
+        <v>4</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" ht="48" spans="1:4">
+      <c r="A34" s="17">
+        <v>5</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" ht="48" spans="1:4">
+      <c r="A35" s="14">
+        <v>6</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A29:D29"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/AI Audit Log_Mai Xuan Tri.xlsx
+++ b/AI Audit Log_Mai Xuan Tri.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Week1" sheetId="1" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" r:id="rId3"/>
+    <sheet name="Week4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="89">
   <si>
     <t>STT</t>
   </si>
@@ -306,6 +307,32 @@
   <si>
     <t>Phản hồi: AI sinh Sequence Diagram: Customer → BookingController → BookingService → ICarRepository.GetAvailableByBranchAsync() → tạo Booking → CarService.UpdateStatusAsync(Rented).
 Quyết định: Chấp nhận. Luồng thể hiện rõ 2 service phối hợp qua UnitOfWork chung.</t>
+  </si>
+  <si>
+    <t>gen cho tôi plantUML sequence diagrams của cái này để tôi check với bài của tôi
+[Use Case: Create Booking and Pay Deposit — mô tả luồng chọn xe, kiểm tra availability, tạo booking, thanh toán deposit]</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI sinh PlantUML Sequence Diagram đầy đủ với 8 participant (Customer, BookingUI, BookingService, PaymentService, Booking, Car, CarRepository, BookingRepository), 2 alt fragment lồng nhau cho car availability và payment result.
+Quyết định: Chấp nhận diagram ban đầu để đối chiếu với bài.</t>
+  </si>
+  <si>
+    <t>cái này nó đang bị thiếu cái lifeline</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI nhận ra diagram thiếu activation bars (lifeline rectangles) — chưa thể hiện khoảng thời gian mỗi participant đang active. Đề xuất 2 cách: autoactivate on (tự động) hoặc activate/deactivate thủ công (chuẩn hơn).
+Quyết định: Người học chọn activate/deactivate thủ công để kiểm soát chính xác từng đoạn.</t>
+  </si>
+  <si>
+    <t>activate / deactivate thủ công — kiểm soát chính xác từng đoạn (chuẩn hơn cho bài)</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI cập nhật diagram với manual activate/deactivate theo đúng nguyên tắc:
+• UI activate xuyên suốt cả flow, deactivate ở cuối mỗi nhánh alt
+• BookingService deactivate ngay sau khi trả về bookingCreated cho UI
+• PaymentService có self-call chargePaymentMethod với activate/deactivate liền nhau
+• CarRepo, BookingRepo chỉ active trong khoảng ngắn mỗi query/save — đúng Repository Pattern (stateless)
+Quyết định: Chấp nhận. Lifeline thể hiện đúng lifecycle của từng participant theo Layered Architecture.</t>
   </si>
 </sst>
 </file>
@@ -334,6 +361,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -358,13 +398,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF2C2C2A"/>
@@ -395,13 +428,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF7B2400"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -569,7 +595,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -584,6 +610,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -835,12 +867,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1082,7 +1129,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1094,206 +1141,218 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1830,192 +1889,192 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:4">
-      <c r="A2" s="6">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:4">
-      <c r="A3" s="6"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="27"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="31"/>
     </row>
     <row r="5" ht="15.75" spans="1:4">
-      <c r="A5" s="6"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="23" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="53" customHeight="1" spans="1:4">
-      <c r="A6" s="6"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1" spans="1:4">
-      <c r="A7" s="3">
+      <c r="A7" s="7">
         <v>2</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" ht="51" customHeight="1" spans="1:4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="25" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="27"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="31"/>
     </row>
     <row r="10" ht="15.75" spans="1:4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="23" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1" spans="1:4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" ht="39.75" customHeight="1" spans="1:4">
-      <c r="A12" s="6">
+      <c r="A12" s="10">
         <v>3</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" ht="53" customHeight="1" spans="1:4">
-      <c r="A13" s="6"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
-      <c r="A14" s="6"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="27"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="31"/>
     </row>
     <row r="15" ht="15.75" spans="1:4">
-      <c r="A15" s="6"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="23" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:4">
-      <c r="A16" s="6"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24" t="s">
+      <c r="A16" s="10"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:4">
-      <c r="A17" s="3">
+      <c r="A17" s="7">
         <v>4</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" ht="26.25" spans="1:4">
-      <c r="A18" s="3"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="25" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="29" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" ht="15.75" spans="1:4">
-      <c r="A19" s="3"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="27"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="31"/>
     </row>
     <row r="20" ht="15.75" spans="1:4">
-      <c r="A20" s="3"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="29" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="33" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" ht="39" customHeight="1" spans="1:4">
-      <c r="A21" s="3"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="30" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="34" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2058,58 +2117,58 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="51.75" spans="1:4">
-      <c r="A2" s="3">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" ht="51.75" spans="1:4">
-      <c r="A3" s="6">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="12" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" ht="51.75" spans="1:4">
-      <c r="A4" s="3">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2117,13 +2176,13 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2131,13 +2190,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2145,381 +2204,381 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
     </row>
     <row r="9" ht="60" spans="1:4">
-      <c r="A9" s="14">
+      <c r="A9" s="18">
         <v>1</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="20" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" ht="48" spans="1:4">
-      <c r="A10" s="17">
+      <c r="A10" s="21">
         <v>2</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="23" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" ht="48" spans="1:4">
-      <c r="A11" s="14">
+      <c r="A11" s="18">
         <v>3</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" ht="48" spans="1:4">
-      <c r="A12" s="17">
+      <c r="A12" s="21">
         <v>4</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="23" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" ht="48" spans="1:4">
-      <c r="A13" s="14">
+      <c r="A13" s="18">
         <v>5</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="20" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" ht="48" spans="1:4">
-      <c r="A14" s="17">
+      <c r="A14" s="21">
         <v>6</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="23" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
     </row>
     <row r="16" ht="48" spans="1:4">
-      <c r="A16" s="17">
+      <c r="A16" s="21">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" ht="48" spans="1:4">
-      <c r="A17" s="14">
+    <row r="17" ht="36" spans="1:4">
+      <c r="A17" s="18">
         <v>2</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="20" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="18" ht="48" spans="1:4">
-      <c r="A18" s="17">
+      <c r="A18" s="21">
         <v>3</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="23" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" ht="48" spans="1:4">
-      <c r="A19" s="14">
+      <c r="A19" s="18">
         <v>4</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" ht="48" spans="1:4">
-      <c r="A20" s="17">
+    <row r="20" ht="36" spans="1:4">
+      <c r="A20" s="21">
         <v>5</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="23" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="21" ht="48" spans="1:4">
-      <c r="A21" s="14">
+      <c r="A21" s="18">
         <v>6</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="20" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
     </row>
     <row r="23" ht="48" spans="1:4">
-      <c r="A23" s="14">
+      <c r="A23" s="18">
         <v>1</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="20" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" ht="48" spans="1:4">
-      <c r="A24" s="17">
+      <c r="A24" s="21">
         <v>2</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="23" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" ht="48" spans="1:4">
-      <c r="A25" s="14">
+      <c r="A25" s="18">
         <v>3</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="20" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" ht="48" spans="1:4">
-      <c r="A26" s="17">
+      <c r="A26" s="21">
         <v>4</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="23" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" ht="48" spans="1:4">
-      <c r="A27" s="14">
+      <c r="A27" s="18">
         <v>5</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="20" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="28" ht="48" spans="1:4">
-      <c r="A28" s="17">
+      <c r="A28" s="21">
         <v>6</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="23" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
     </row>
     <row r="30" ht="48" spans="1:4">
-      <c r="A30" s="17">
+      <c r="A30" s="21">
         <v>1</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="23" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="31" ht="36" spans="1:4">
-      <c r="A31" s="14">
+      <c r="A31" s="18">
         <v>2</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="20" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="32" ht="48" spans="1:4">
-      <c r="A32" s="17">
+      <c r="A32" s="21">
         <v>3</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="33" ht="60" spans="1:4">
-      <c r="A33" s="14">
+      <c r="A33" s="18">
         <v>4</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="34" ht="48" spans="1:4">
-      <c r="A34" s="17">
+      <c r="A34" s="21">
         <v>5</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="23" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="35" ht="48" spans="1:4">
-      <c r="A35" s="14">
+      <c r="A35" s="18">
         <v>6</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="20" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2533,4 +2592,78 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="9.85714285714286" customWidth="1"/>
+    <col min="2" max="2" width="38.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="25.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="119.6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="50" customHeight="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="141" customHeight="1" spans="1:4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="1:4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" ht="106" customHeight="1" spans="1:4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>